--- a/Liste clients.xlsx
+++ b/Liste clients.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvannlandure/Desktop/Finistech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E50699-2C22-264F-8381-0473D5DDB8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D330A1C8-0A29-6B49-95BC-3F9DE633B608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="740" windowWidth="28040" windowHeight="17140" xr2:uid="{55C2120D-E7B2-4249-9BB3-0C70A104EAEB}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{55C2120D-E7B2-4249-9BB3-0C70A104EAEB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Exploitations agricoles" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -35,9 +35,353 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+  <si>
+    <t>ID_Agri</t>
+  </si>
+  <si>
+    <t>Nom_Exploitation</t>
+  </si>
+  <si>
+    <t>Type_Produit</t>
+  </si>
+  <si>
+    <t>Code_Postal</t>
+  </si>
+  <si>
+    <t>Capacite_Annuelle</t>
+  </si>
+  <si>
+    <t>Cout_Production</t>
+  </si>
+  <si>
+    <t>Score_Credit</t>
+  </si>
+  <si>
+    <t>Stockage_Max</t>
+  </si>
+  <si>
+    <t>Ferme du Kermin</t>
+  </si>
+  <si>
+    <t>AGRI001</t>
+  </si>
+  <si>
+    <t>Lait</t>
+  </si>
+  <si>
+    <t>0.38</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>GAEC de l'Argoat</t>
+  </si>
+  <si>
+    <t>AGRI002</t>
+  </si>
+  <si>
+    <t>Porc</t>
+  </si>
+  <si>
+    <t>1.42</t>
+  </si>
+  <si>
+    <t>0.85</t>
+  </si>
+  <si>
+    <t>EARL des Embruns</t>
+  </si>
+  <si>
+    <t>AGRI003</t>
+  </si>
+  <si>
+    <t>Blé tendre</t>
+  </si>
+  <si>
+    <t>0.78</t>
+  </si>
+  <si>
+    <t>Elevage du Trégor</t>
+  </si>
+  <si>
+    <t>AGRI004</t>
+  </si>
+  <si>
+    <t>0.41</t>
+  </si>
+  <si>
+    <t>0.95</t>
+  </si>
+  <si>
+    <t>AGRI005</t>
+  </si>
+  <si>
+    <t>Maïs</t>
+  </si>
+  <si>
+    <t>0.88</t>
+  </si>
+  <si>
+    <t>Ferme de Keriolet</t>
+  </si>
+  <si>
+    <t>AGRI006</t>
+  </si>
+  <si>
+    <t>1.38</t>
+  </si>
+  <si>
+    <t>0.91</t>
+  </si>
+  <si>
+    <t>SCEA du Menhir</t>
+  </si>
+  <si>
+    <t>AGRI007</t>
+  </si>
+  <si>
+    <t>0.82</t>
+  </si>
+  <si>
+    <t>La Laiterie d'Armor</t>
+  </si>
+  <si>
+    <t>AGRI008</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>0.89</t>
+  </si>
+  <si>
+    <t>Terres d'Iroise</t>
+  </si>
+  <si>
+    <t>AGRI009</t>
+  </si>
+  <si>
+    <t>Orge</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>GAEC de Brocéliande</t>
+  </si>
+  <si>
+    <t>AGRI010</t>
+  </si>
+  <si>
+    <t>0.42</t>
+  </si>
+  <si>
+    <t>0.87</t>
+  </si>
+  <si>
+    <t>Les Plaines de l'Ouest</t>
+  </si>
+  <si>
+    <t>Ferme de la Baie 101</t>
+  </si>
+  <si>
+    <t>AGRI101</t>
+  </si>
+  <si>
+    <t>GAEC du Golfe 102</t>
+  </si>
+  <si>
+    <t>AGRI102</t>
+  </si>
+  <si>
+    <t>1.44</t>
+  </si>
+  <si>
+    <t>SCEA des Bruyères 103</t>
+  </si>
+  <si>
+    <t>AGRI103</t>
+  </si>
+  <si>
+    <t>162.5</t>
+  </si>
+  <si>
+    <t>EARL du Ponant 104</t>
+  </si>
+  <si>
+    <t>AGRI104</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>Ferme de la Lande 105</t>
+  </si>
+  <si>
+    <t>AGRI105</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>GAEC de l'Océan 106</t>
+  </si>
+  <si>
+    <t>AGRI106</t>
+  </si>
+  <si>
+    <t>1.39</t>
+  </si>
+  <si>
+    <t>SCEA de Ker-Ys 107</t>
+  </si>
+  <si>
+    <t>AGRI107</t>
+  </si>
+  <si>
+    <t>169.0</t>
+  </si>
+  <si>
+    <t>0.77</t>
+  </si>
+  <si>
+    <t>EARL des Ajoncs 108</t>
+  </si>
+  <si>
+    <t>AGRI108</t>
+  </si>
+  <si>
+    <t>153.5</t>
+  </si>
+  <si>
+    <t>0.84</t>
+  </si>
+  <si>
+    <t>Ferme du Val 109</t>
+  </si>
+  <si>
+    <t>AGRI109</t>
+  </si>
+  <si>
+    <t>GAEC de la Ria 110</t>
+  </si>
+  <si>
+    <t>AGRI110</t>
+  </si>
+  <si>
+    <t>SCEA du Hêtre 111</t>
+  </si>
+  <si>
+    <t>AGRI111</t>
+  </si>
+  <si>
+    <t>158.0</t>
+  </si>
+  <si>
+    <t>0.96</t>
+  </si>
+  <si>
+    <t>EARL du Grand Air 112</t>
+  </si>
+  <si>
+    <t>AGRI112</t>
+  </si>
+  <si>
+    <t>161.0</t>
+  </si>
+  <si>
+    <t>0.81</t>
+  </si>
+  <si>
+    <t>Ferme du Marais 113</t>
+  </si>
+  <si>
+    <t>AGRI113</t>
+  </si>
+  <si>
+    <t>0.83</t>
+  </si>
+  <si>
+    <t>GAEC Pen-Ar-Bed 114</t>
+  </si>
+  <si>
+    <t>AGRI114</t>
+  </si>
+  <si>
+    <t>1.37</t>
+  </si>
+  <si>
+    <t>0.93</t>
+  </si>
+  <si>
+    <t>SCEA de Kerlouan 115</t>
+  </si>
+  <si>
+    <t>AGRI115</t>
+  </si>
+  <si>
+    <t>174.0</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>EARL du Moulin 116</t>
+  </si>
+  <si>
+    <t>AGRI116</t>
+  </si>
+  <si>
+    <t>151.0</t>
+  </si>
+  <si>
+    <t>0.9</t>
+  </si>
+  <si>
+    <t>Ferme Sainte-Anne 117</t>
+  </si>
+  <si>
+    <t>AGRI117</t>
+  </si>
+  <si>
+    <t>GAEC de Glénan 118</t>
+  </si>
+  <si>
+    <t>AGRI118</t>
+  </si>
+  <si>
+    <t>1.46</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>SCEA de la Garenne 119</t>
+  </si>
+  <si>
+    <t>AGRI119</t>
+  </si>
+  <si>
+    <t>166.0</t>
+  </si>
+  <si>
+    <t>EARL de Cornouaille 120</t>
+  </si>
+  <si>
+    <t>AGRI120</t>
+  </si>
+  <si>
+    <t>0.97</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -45,13 +389,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -66,8 +429,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +767,826 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F35F8F1-F6FF-1349-ABEE-5648D6B7BABE}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="1">
+        <v>29200</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1">
+        <v>850000</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="1">
+        <v>22400</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="1">
+        <v>29120</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="1">
+        <v>450</v>
+      </c>
+      <c r="F4" s="1">
+        <v>165</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22300</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <v>600000</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1">
+        <v>56800</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1">
+        <v>800</v>
+      </c>
+      <c r="F6" s="1">
+        <v>155</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="1">
+        <v>29900</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2500</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="1">
+        <v>35500</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F8" s="1">
+        <v>162</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="1">
+        <v>22100</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1100000</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="1">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="1">
+        <v>29217</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1">
+        <v>300</v>
+      </c>
+      <c r="F10" s="1">
+        <v>158</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1">
+        <v>35380</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1">
+        <v>750000</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="1">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12">
+        <v>29100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>950000</v>
+      </c>
+      <c r="F12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13">
+        <v>56000</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>1350</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>22200</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>720</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H14">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15">
+        <v>29200</v>
+      </c>
+      <c r="D15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15">
+        <v>1100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
+        <v>35600</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>820000</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>29120</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>2100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>29000</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>540</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19">
+        <v>22400</v>
+      </c>
+      <c r="D19" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19">
+        <v>1400</v>
+      </c>
+      <c r="F19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" t="s">
+        <v>73</v>
+      </c>
+      <c r="H19">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>35000</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20">
+        <v>1050000</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>76</v>
+      </c>
+      <c r="B21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21">
+        <v>56550</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21">
+        <v>1600</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22">
+        <v>22100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22">
+        <v>980</v>
+      </c>
+      <c r="F22" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23">
+        <v>29600</v>
+      </c>
+      <c r="D23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23">
+        <v>850</v>
+      </c>
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24">
+        <v>35120</v>
+      </c>
+      <c r="D24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24">
+        <v>760000</v>
+      </c>
+      <c r="F24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25">
+        <v>29200</v>
+      </c>
+      <c r="D25" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25">
+        <v>2800</v>
+      </c>
+      <c r="F25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" t="s">
+        <v>92</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26">
+        <v>29890</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26">
+        <v>410</v>
+      </c>
+      <c r="F26" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27">
+        <v>56100</v>
+      </c>
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27">
+        <v>1650</v>
+      </c>
+      <c r="F27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28">
+        <v>22000</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>990000</v>
+      </c>
+      <c r="F28" t="s">
+        <v>38</v>
+      </c>
+      <c r="G28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29">
+        <v>29170</v>
+      </c>
+      <c r="D29" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29">
+        <v>1250</v>
+      </c>
+      <c r="F29" t="s">
+        <v>105</v>
+      </c>
+      <c r="G29" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30">
+        <v>35300</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30">
+        <v>670</v>
+      </c>
+      <c r="F30" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C31">
+        <v>29000</v>
+      </c>
+      <c r="D31" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>1180000</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31">
+        <v>95000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Liste clients.xlsx
+++ b/Liste clients.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yvannlandure/Desktop/Finistech/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D330A1C8-0A29-6B49-95BC-3F9DE633B608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280AF547-C564-3E49-B521-18BEA4CC60A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{55C2120D-E7B2-4249-9BB3-0C70A104EAEB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="283">
   <si>
     <t>ID_Agri</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Stockage_Max</t>
   </si>
   <si>
-    <t>Ferme du Kermin</t>
-  </si>
-  <si>
     <t>AGRI001</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
     <t>0.92</t>
   </si>
   <si>
-    <t>GAEC de l'Argoat</t>
-  </si>
-  <si>
     <t>AGRI002</t>
   </si>
   <si>
@@ -92,9 +86,6 @@
     <t>0.85</t>
   </si>
   <si>
-    <t>EARL des Embruns</t>
-  </si>
-  <si>
     <t>AGRI003</t>
   </si>
   <si>
@@ -104,9 +95,6 @@
     <t>0.78</t>
   </si>
   <si>
-    <t>Elevage du Trégor</t>
-  </si>
-  <si>
     <t>AGRI004</t>
   </si>
   <si>
@@ -125,9 +113,6 @@
     <t>0.88</t>
   </si>
   <si>
-    <t>Ferme de Keriolet</t>
-  </si>
-  <si>
     <t>AGRI006</t>
   </si>
   <si>
@@ -137,18 +122,12 @@
     <t>0.91</t>
   </si>
   <si>
-    <t>SCEA du Menhir</t>
-  </si>
-  <si>
     <t>AGRI007</t>
   </si>
   <si>
     <t>0.82</t>
   </si>
   <si>
-    <t>La Laiterie d'Armor</t>
-  </si>
-  <si>
     <t>AGRI008</t>
   </si>
   <si>
@@ -158,21 +137,12 @@
     <t>0.89</t>
   </si>
   <si>
-    <t>Terres d'Iroise</t>
-  </si>
-  <si>
     <t>AGRI009</t>
   </si>
   <si>
-    <t>Orge</t>
-  </si>
-  <si>
     <t>0.94</t>
   </si>
   <si>
-    <t>GAEC de Brocéliande</t>
-  </si>
-  <si>
     <t>AGRI010</t>
   </si>
   <si>
@@ -182,199 +152,739 @@
     <t>0.87</t>
   </si>
   <si>
-    <t>Les Plaines de l'Ouest</t>
-  </si>
-  <si>
-    <t>Ferme de la Baie 101</t>
-  </si>
-  <si>
-    <t>AGRI101</t>
-  </si>
-  <si>
-    <t>GAEC du Golfe 102</t>
-  </si>
-  <si>
-    <t>AGRI102</t>
-  </si>
-  <si>
     <t>1.44</t>
   </si>
   <si>
-    <t>SCEA des Bruyères 103</t>
-  </si>
-  <si>
-    <t>AGRI103</t>
-  </si>
-  <si>
-    <t>162.5</t>
-  </si>
-  <si>
-    <t>EARL du Ponant 104</t>
-  </si>
-  <si>
-    <t>AGRI104</t>
-  </si>
-  <si>
     <t>157.0</t>
   </si>
   <si>
-    <t>Ferme de la Lande 105</t>
-  </si>
-  <si>
-    <t>AGRI105</t>
-  </si>
-  <si>
     <t>0.86</t>
   </si>
   <si>
-    <t>GAEC de l'Océan 106</t>
-  </si>
-  <si>
-    <t>AGRI106</t>
-  </si>
-  <si>
     <t>1.39</t>
   </si>
   <si>
-    <t>SCEA de Ker-Ys 107</t>
-  </si>
-  <si>
-    <t>AGRI107</t>
-  </si>
-  <si>
     <t>169.0</t>
   </si>
   <si>
     <t>0.77</t>
   </si>
   <si>
-    <t>EARL des Ajoncs 108</t>
-  </si>
-  <si>
-    <t>AGRI108</t>
-  </si>
-  <si>
-    <t>153.5</t>
-  </si>
-  <si>
     <t>0.84</t>
   </si>
   <si>
-    <t>Ferme du Val 109</t>
-  </si>
-  <si>
-    <t>AGRI109</t>
-  </si>
-  <si>
-    <t>GAEC de la Ria 110</t>
-  </si>
-  <si>
-    <t>AGRI110</t>
-  </si>
-  <si>
-    <t>SCEA du Hêtre 111</t>
-  </si>
-  <si>
-    <t>AGRI111</t>
-  </si>
-  <si>
     <t>158.0</t>
   </si>
   <si>
     <t>0.96</t>
   </si>
   <si>
-    <t>EARL du Grand Air 112</t>
-  </si>
-  <si>
-    <t>AGRI112</t>
-  </si>
-  <si>
     <t>161.0</t>
   </si>
   <si>
     <t>0.81</t>
   </si>
   <si>
-    <t>Ferme du Marais 113</t>
-  </si>
-  <si>
-    <t>AGRI113</t>
-  </si>
-  <si>
     <t>0.83</t>
   </si>
   <si>
-    <t>GAEC Pen-Ar-Bed 114</t>
-  </si>
-  <si>
-    <t>AGRI114</t>
-  </si>
-  <si>
     <t>1.37</t>
   </si>
   <si>
     <t>0.93</t>
   </si>
   <si>
-    <t>SCEA de Kerlouan 115</t>
-  </si>
-  <si>
-    <t>AGRI115</t>
-  </si>
-  <si>
-    <t>174.0</t>
-  </si>
-  <si>
     <t>0.75</t>
   </si>
   <si>
-    <t>EARL du Moulin 116</t>
-  </si>
-  <si>
-    <t>AGRI116</t>
-  </si>
-  <si>
     <t>151.0</t>
   </si>
   <si>
     <t>0.9</t>
   </si>
   <si>
-    <t>Ferme Sainte-Anne 117</t>
-  </si>
-  <si>
-    <t>AGRI117</t>
-  </si>
-  <si>
-    <t>GAEC de Glénan 118</t>
-  </si>
-  <si>
-    <t>AGRI118</t>
-  </si>
-  <si>
     <t>1.46</t>
   </si>
   <si>
     <t>0.8</t>
   </si>
   <si>
-    <t>SCEA de la Garenne 119</t>
-  </si>
-  <si>
-    <t>AGRI119</t>
-  </si>
-  <si>
     <t>166.0</t>
   </si>
   <si>
-    <t>EARL de Cornouaille 120</t>
-  </si>
-  <si>
-    <t>AGRI120</t>
-  </si>
-  <si>
     <t>0.97</t>
+  </si>
+  <si>
+    <t>Ferme du Léon 1</t>
+  </si>
+  <si>
+    <t>GAEC Armorique 2</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>SCEA Brocéliande 3</t>
+  </si>
+  <si>
+    <t>168.0</t>
+  </si>
+  <si>
+    <t>Terres d'Iroise 4</t>
+  </si>
+  <si>
+    <t>155.0</t>
+  </si>
+  <si>
+    <t>Elevage du Trégor 5</t>
+  </si>
+  <si>
+    <t>0.4</t>
+  </si>
+  <si>
+    <t>Ferme de Keriolet 6</t>
+  </si>
+  <si>
+    <t>EARL du Menez 7</t>
+  </si>
+  <si>
+    <t>172.0</t>
+  </si>
+  <si>
+    <t>GAEC de l'Argoat 8</t>
+  </si>
+  <si>
+    <t>SCEA du Menhir 9</t>
+  </si>
+  <si>
+    <t>152.0</t>
+  </si>
+  <si>
+    <t>Ferme de Bel-Air 10</t>
+  </si>
+  <si>
+    <t>EARL Kerval 11</t>
+  </si>
+  <si>
+    <t>AGRI011</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>Ferme d'Iroise 12</t>
+  </si>
+  <si>
+    <t>AGRI012</t>
+  </si>
+  <si>
+    <t>160.0</t>
+  </si>
+  <si>
+    <t>GAEC du Trégor 13</t>
+  </si>
+  <si>
+    <t>AGRI013</t>
+  </si>
+  <si>
+    <t>SCEA Armor 14</t>
+  </si>
+  <si>
+    <t>AGRI014</t>
+  </si>
+  <si>
+    <t>Ferme du Menez 15</t>
+  </si>
+  <si>
+    <t>AGRI015</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>EARL de Brocéliande 16</t>
+  </si>
+  <si>
+    <t>AGRI016</t>
+  </si>
+  <si>
+    <t>0.37</t>
+  </si>
+  <si>
+    <t>GAEC de l'Oust 17</t>
+  </si>
+  <si>
+    <t>AGRI017</t>
+  </si>
+  <si>
+    <t>165.0</t>
+  </si>
+  <si>
+    <t>SCEA d'Iroise 18</t>
+  </si>
+  <si>
+    <t>AGRI018</t>
+  </si>
+  <si>
+    <t>154.0</t>
+  </si>
+  <si>
+    <t>Ferme du Trégor 19</t>
+  </si>
+  <si>
+    <t>AGRI019</t>
+  </si>
+  <si>
+    <t>EARL du Léon 20</t>
+  </si>
+  <si>
+    <t>AGRI020</t>
+  </si>
+  <si>
+    <t>GAEC de Keriolet 21</t>
+  </si>
+  <si>
+    <t>AGRI021</t>
+  </si>
+  <si>
+    <t>163.0</t>
+  </si>
+  <si>
+    <t>SCEA de Bel-Air 22</t>
+  </si>
+  <si>
+    <t>AGRI022</t>
+  </si>
+  <si>
+    <t>156.0</t>
+  </si>
+  <si>
+    <t>Ferme de l'Argoat 23</t>
+  </si>
+  <si>
+    <t>AGRI023</t>
+  </si>
+  <si>
+    <t>EARL du Menhir 24</t>
+  </si>
+  <si>
+    <t>AGRI024</t>
+  </si>
+  <si>
+    <t>GAEC d'Armor 25</t>
+  </si>
+  <si>
+    <t>AGRI025</t>
+  </si>
+  <si>
+    <t>159.0</t>
+  </si>
+  <si>
+    <t>SCEA Kerval 26</t>
+  </si>
+  <si>
+    <t>AGRI026</t>
+  </si>
+  <si>
+    <t>Ferme de Brocéliande 27</t>
+  </si>
+  <si>
+    <t>AGRI027</t>
+  </si>
+  <si>
+    <t>153.0</t>
+  </si>
+  <si>
+    <t>EARL d'Iroise 28</t>
+  </si>
+  <si>
+    <t>AGRI028</t>
+  </si>
+  <si>
+    <t>0.79</t>
+  </si>
+  <si>
+    <t>GAEC du Menez 29</t>
+  </si>
+  <si>
+    <t>AGRI029</t>
+  </si>
+  <si>
+    <t>SCEA du Trégor 30</t>
+  </si>
+  <si>
+    <t>AGRI030</t>
+  </si>
+  <si>
+    <t>167.0</t>
+  </si>
+  <si>
+    <t>Ferme du Léon 31</t>
+  </si>
+  <si>
+    <t>AGRI031</t>
+  </si>
+  <si>
+    <t>EARL de Keriolet 32</t>
+  </si>
+  <si>
+    <t>AGRI032</t>
+  </si>
+  <si>
+    <t>GAEC de Bel-Air 33</t>
+  </si>
+  <si>
+    <t>AGRI033</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>SCEA de l'Argoat 34</t>
+  </si>
+  <si>
+    <t>AGRI034</t>
+  </si>
+  <si>
+    <t>170.0</t>
+  </si>
+  <si>
+    <t>Ferme du Menhir 35</t>
+  </si>
+  <si>
+    <t>AGRI035</t>
+  </si>
+  <si>
+    <t>EARL d'Armor 36</t>
+  </si>
+  <si>
+    <t>AGRI036</t>
+  </si>
+  <si>
+    <t>GAEC Kerval 37</t>
+  </si>
+  <si>
+    <t>AGRI037</t>
+  </si>
+  <si>
+    <t>1.47</t>
+  </si>
+  <si>
+    <t>0.76</t>
+  </si>
+  <si>
+    <t>SCEA de Brocéliande 38</t>
+  </si>
+  <si>
+    <t>AGRI038</t>
+  </si>
+  <si>
+    <t>Ferme d'Iroise 39</t>
+  </si>
+  <si>
+    <t>AGRI039</t>
+  </si>
+  <si>
+    <t>162.0</t>
+  </si>
+  <si>
+    <t>EARL du Menez 40</t>
+  </si>
+  <si>
+    <t>AGRI040</t>
+  </si>
+  <si>
+    <t>GAEC du Trégor 41</t>
+  </si>
+  <si>
+    <t>AGRI041</t>
+  </si>
+  <si>
+    <t>SCEA du Léon 42</t>
+  </si>
+  <si>
+    <t>AGRI042</t>
+  </si>
+  <si>
+    <t>1.36</t>
+  </si>
+  <si>
+    <t>Ferme de Keriolet 43</t>
+  </si>
+  <si>
+    <t>AGRI043</t>
+  </si>
+  <si>
+    <t>175.0</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>EARL de Bel-Air 44</t>
+  </si>
+  <si>
+    <t>AGRI044</t>
+  </si>
+  <si>
+    <t>GAEC de l'Argoat 45</t>
+  </si>
+  <si>
+    <t>AGRI045</t>
+  </si>
+  <si>
+    <t>150.0</t>
+  </si>
+  <si>
+    <t>SCEA du Menhir 46</t>
+  </si>
+  <si>
+    <t>AGRI046</t>
+  </si>
+  <si>
+    <t>Ferme d'Armor 47</t>
+  </si>
+  <si>
+    <t>AGRI047</t>
+  </si>
+  <si>
+    <t>EARL Kerval 48</t>
+  </si>
+  <si>
+    <t>AGRI048</t>
+  </si>
+  <si>
+    <t>GAEC de Brocéliande 49</t>
+  </si>
+  <si>
+    <t>AGRI049</t>
+  </si>
+  <si>
+    <t>SCEA d'Iroise 50</t>
+  </si>
+  <si>
+    <t>AGRI050</t>
+  </si>
+  <si>
+    <t>Ferme du Menez 51</t>
+  </si>
+  <si>
+    <t>AGRI051</t>
+  </si>
+  <si>
+    <t>EARL du Trégor 52</t>
+  </si>
+  <si>
+    <t>AGRI052</t>
+  </si>
+  <si>
+    <t>GAEC du Léon 53</t>
+  </si>
+  <si>
+    <t>AGRI053</t>
+  </si>
+  <si>
+    <t>SCEA de Keriolet 54</t>
+  </si>
+  <si>
+    <t>AGRI054</t>
+  </si>
+  <si>
+    <t>Ferme de Bel-Air 55</t>
+  </si>
+  <si>
+    <t>AGRI055</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>EARL de l'Argoat 56</t>
+  </si>
+  <si>
+    <t>AGRI056</t>
+  </si>
+  <si>
+    <t>164.0</t>
+  </si>
+  <si>
+    <t>GAEC du Menhir 57</t>
+  </si>
+  <si>
+    <t>AGRI057</t>
+  </si>
+  <si>
+    <t>SCEA d'Armor 58</t>
+  </si>
+  <si>
+    <t>AGRI058</t>
+  </si>
+  <si>
+    <t>Ferme Kerval 59</t>
+  </si>
+  <si>
+    <t>AGRI059</t>
+  </si>
+  <si>
+    <t>EARL de Brocéliande 60</t>
+  </si>
+  <si>
+    <t>AGRI060</t>
+  </si>
+  <si>
+    <t>GAEC d'Iroise 61</t>
+  </si>
+  <si>
+    <t>AGRI061</t>
+  </si>
+  <si>
+    <t>SCEA du Menez 62</t>
+  </si>
+  <si>
+    <t>AGRI062</t>
+  </si>
+  <si>
+    <t>Ferme du Trégor 63</t>
+  </si>
+  <si>
+    <t>AGRI063</t>
+  </si>
+  <si>
+    <t>EARL du Léon 64</t>
+  </si>
+  <si>
+    <t>AGRI064</t>
+  </si>
+  <si>
+    <t>173.0</t>
+  </si>
+  <si>
+    <t>GAEC de Keriolet 65</t>
+  </si>
+  <si>
+    <t>AGRI065</t>
+  </si>
+  <si>
+    <t>SCEA de Bel-Air 66</t>
+  </si>
+  <si>
+    <t>AGRI066</t>
+  </si>
+  <si>
+    <t>Ferme de l'Argoat 67</t>
+  </si>
+  <si>
+    <t>AGRI067</t>
+  </si>
+  <si>
+    <t>1.43</t>
+  </si>
+  <si>
+    <t>EARL du Menhir 68</t>
+  </si>
+  <si>
+    <t>AGRI068</t>
+  </si>
+  <si>
+    <t>GAEC d'Armor 69</t>
+  </si>
+  <si>
+    <t>AGRI069</t>
+  </si>
+  <si>
+    <t>SCEA Kerval 70</t>
+  </si>
+  <si>
+    <t>AGRI070</t>
+  </si>
+  <si>
+    <t>Ferme de Brocéliande 71</t>
+  </si>
+  <si>
+    <t>AGRI071</t>
+  </si>
+  <si>
+    <t>EARL d'Iroise 72</t>
+  </si>
+  <si>
+    <t>AGRI072</t>
+  </si>
+  <si>
+    <t>171.0</t>
+  </si>
+  <si>
+    <t>GAEC du Menez 73</t>
+  </si>
+  <si>
+    <t>AGRI073</t>
+  </si>
+  <si>
+    <t>SCEA du Trégor 74</t>
+  </si>
+  <si>
+    <t>AGRI074</t>
+  </si>
+  <si>
+    <t>Ferme du Léon 75</t>
+  </si>
+  <si>
+    <t>AGRI075</t>
+  </si>
+  <si>
+    <t>EARL de Keriolet 76</t>
+  </si>
+  <si>
+    <t>AGRI076</t>
+  </si>
+  <si>
+    <t>GAEC de Bel-Air 77</t>
+  </si>
+  <si>
+    <t>AGRI077</t>
+  </si>
+  <si>
+    <t>SCEA de l'Argoat 78</t>
+  </si>
+  <si>
+    <t>AGRI078</t>
+  </si>
+  <si>
+    <t>Ferme du Menhir 79</t>
+  </si>
+  <si>
+    <t>AGRI079</t>
+  </si>
+  <si>
+    <t>EARL d'Armor 80</t>
+  </si>
+  <si>
+    <t>AGRI080</t>
+  </si>
+  <si>
+    <t>GAEC Kerval 81</t>
+  </si>
+  <si>
+    <t>AGRI081</t>
+  </si>
+  <si>
+    <t>SCEA de Brocéliande 82</t>
+  </si>
+  <si>
+    <t>AGRI082</t>
+  </si>
+  <si>
+    <t>Ferme d'Iroise 83</t>
+  </si>
+  <si>
+    <t>AGRI083</t>
+  </si>
+  <si>
+    <t>EARL du Menez 84</t>
+  </si>
+  <si>
+    <t>AGRI084</t>
+  </si>
+  <si>
+    <t>GAEC du Trégor 85</t>
+  </si>
+  <si>
+    <t>AGRI085</t>
+  </si>
+  <si>
+    <t>SCEA du Léon 86</t>
+  </si>
+  <si>
+    <t>AGRI086</t>
+  </si>
+  <si>
+    <t>Ferme de Keriolet 87</t>
+  </si>
+  <si>
+    <t>AGRI087</t>
+  </si>
+  <si>
+    <t>EARL de Bel-Air 88</t>
+  </si>
+  <si>
+    <t>AGRI088</t>
+  </si>
+  <si>
+    <t>GAEC de l'Argoat 89</t>
+  </si>
+  <si>
+    <t>AGRI089</t>
+  </si>
+  <si>
+    <t>SCEA du Menhir 90</t>
+  </si>
+  <si>
+    <t>AGRI090</t>
+  </si>
+  <si>
+    <t>Ferme d'Armor 91</t>
+  </si>
+  <si>
+    <t>AGRI091</t>
+  </si>
+  <si>
+    <t>EARL Kerval 92</t>
+  </si>
+  <si>
+    <t>AGRI092</t>
+  </si>
+  <si>
+    <t>GAEC de Brocéliande 93</t>
+  </si>
+  <si>
+    <t>AGRI093</t>
+  </si>
+  <si>
+    <t>SCEA d'Iroise 94</t>
+  </si>
+  <si>
+    <t>AGRI094</t>
+  </si>
+  <si>
+    <t>Ferme du Menez 95</t>
+  </si>
+  <si>
+    <t>AGRI095</t>
+  </si>
+  <si>
+    <t>0.73</t>
+  </si>
+  <si>
+    <t>EARL du Trégor 96</t>
+  </si>
+  <si>
+    <t>AGRI096</t>
+  </si>
+  <si>
+    <t>GAEC du Léon 97</t>
+  </si>
+  <si>
+    <t>AGRI097</t>
+  </si>
+  <si>
+    <t>SCEA de Keriolet 98</t>
+  </si>
+  <si>
+    <t>AGRI098</t>
+  </si>
+  <si>
+    <t>0.98</t>
+  </si>
+  <si>
+    <t>Ferme de Bel-Air 99</t>
+  </si>
+  <si>
+    <t>AGRI099</t>
+  </si>
+  <si>
+    <t>EARL de l'Argoat 100</t>
+  </si>
+  <si>
+    <t>AGRI100</t>
   </si>
 </sst>
 </file>
@@ -767,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F35F8F1-F6FF-1349-ABEE-5648D6B7BABE}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" bestFit="1" customWidth="1"/>
@@ -808,25 +1318,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>29200</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1">
         <v>850000</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="H2" s="1">
         <v>50000</v>
@@ -834,25 +1344,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>22400</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1">
+        <v>1500</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1200</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
@@ -860,103 +1370,103 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1">
+        <v>35000</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1">
+        <v>600</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="1">
-        <v>29120</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1">
-        <v>450</v>
-      </c>
-      <c r="F4" s="1">
-        <v>165</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" s="1">
-        <v>600</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1">
+        <v>29120</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1">
-        <v>22300</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E5" s="1">
-        <v>600000</v>
+        <v>1200</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1">
-        <v>30000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1">
-        <v>56800</v>
+        <v>22100</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>800</v>
-      </c>
-      <c r="F6" s="1">
-        <v>155</v>
+        <v>920000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H6" s="1">
-        <v>1000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1">
-        <v>29900</v>
+        <v>29000</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E7" s="1">
-        <v>2500</v>
+        <v>2200</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -964,103 +1474,103 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
-        <v>35500</v>
+        <v>29600</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E8" s="1">
-        <v>1200</v>
-      </c>
-      <c r="F8" s="1">
-        <v>162</v>
+        <v>450</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1">
-        <v>1500</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
-        <v>22100</v>
+        <v>22300</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1">
         <v>1100000</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H9" s="1">
-        <v>80000</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
-        <v>29217</v>
+        <v>56000</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1">
-        <v>300</v>
-      </c>
-      <c r="F10" s="1">
-        <v>158</v>
+        <v>1800</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H10" s="1">
-        <v>400</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1">
-        <v>35380</v>
+        <v>35700</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1">
         <v>750000</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H11" s="1">
         <v>45000</v>
@@ -1068,363 +1578,363 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C12">
-        <v>29100</v>
+        <v>56800</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E12">
-        <v>950000</v>
+        <v>1100</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H12">
-        <v>70000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13">
+        <v>29217</v>
+      </c>
+      <c r="D13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13">
+        <v>850</v>
+      </c>
+      <c r="F13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
         <v>51</v>
       </c>
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13">
-        <v>56000</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13">
-        <v>1350</v>
-      </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G13" t="s">
-        <v>35</v>
-      </c>
       <c r="H13">
-        <v>0</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C14">
-        <v>22200</v>
+        <v>22100</v>
       </c>
       <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14">
+        <v>680000</v>
+      </c>
+      <c r="F14" t="s">
         <v>20</v>
       </c>
-      <c r="E14">
-        <v>720</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="H14">
-        <v>1200</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C15">
-        <v>29200</v>
+        <v>22400</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E15">
-        <v>1100</v>
+        <v>950</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G15" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="H15">
-        <v>1800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="C16">
-        <v>35600</v>
+        <v>29600</v>
       </c>
       <c r="D16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E16">
-        <v>820000</v>
+        <v>3000</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H16">
-        <v>45000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C17">
-        <v>29120</v>
+        <v>35000</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E17">
-        <v>2100</v>
+        <v>1200000</v>
       </c>
       <c r="F17" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C18">
-        <v>29000</v>
+        <v>56800</v>
       </c>
       <c r="D18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E18">
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="H18">
-        <v>950</v>
+        <v>900</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C19">
-        <v>22400</v>
+        <v>29000</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19">
         <v>1400</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="H19">
-        <v>2300</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="C20">
-        <v>35000</v>
+        <v>22300</v>
       </c>
       <c r="D20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>1050000</v>
+        <v>1800</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="H20">
-        <v>80000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="C21">
-        <v>56550</v>
+        <v>29200</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E21">
-        <v>1600</v>
+        <v>890000</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>55000</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C22">
-        <v>22100</v>
+        <v>29000</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E22">
-        <v>980</v>
+        <v>720</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="H22">
-        <v>1800</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C23">
-        <v>29600</v>
+        <v>35700</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="H23">
-        <v>1300</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C24">
-        <v>35120</v>
+        <v>22400</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24">
-        <v>760000</v>
+        <v>950000</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="H24">
-        <v>38000</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="C25">
-        <v>29200</v>
+        <v>56000</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>2800</v>
+        <v>2500</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -1432,103 +1942,103 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C26">
-        <v>29890</v>
+        <v>22100</v>
       </c>
       <c r="D26" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E26">
-        <v>410</v>
+        <v>900</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="H26">
-        <v>650</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C27">
-        <v>56100</v>
+        <v>56800</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>1650</v>
+        <v>1050000</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="H27">
-        <v>2800</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C28">
-        <v>22000</v>
+        <v>35000</v>
       </c>
       <c r="D28" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E28">
-        <v>990000</v>
+        <v>1300</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="H28">
-        <v>72000</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="C29">
-        <v>29170</v>
+        <v>29120</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E29">
-        <v>1250</v>
+        <v>1400</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -1536,54 +2046,1874 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B30" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C30">
-        <v>35300</v>
+        <v>29600</v>
       </c>
       <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
+        <v>780000</v>
+      </c>
+      <c r="F30" t="s">
         <v>20</v>
       </c>
-      <c r="E30">
-        <v>670</v>
-      </c>
-      <c r="F30" t="s">
-        <v>109</v>
-      </c>
       <c r="G30" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H30">
-        <v>1100</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="C31">
+        <v>22300</v>
+      </c>
+      <c r="D31" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31">
+        <v>640</v>
+      </c>
+      <c r="F31" t="s">
+        <v>126</v>
+      </c>
+      <c r="G31" t="s">
+        <v>48</v>
+      </c>
+      <c r="H31">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32">
+        <v>29200</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32">
+        <v>1600</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33">
         <v>29000</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33">
+        <v>910000</v>
+      </c>
+      <c r="F33" t="s">
+        <v>67</v>
+      </c>
+      <c r="G33" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33">
+        <v>62000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34">
+        <v>35700</v>
+      </c>
+      <c r="D34" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34">
+        <v>2000</v>
+      </c>
+      <c r="F34" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>134</v>
+      </c>
+      <c r="B35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C35">
+        <v>22400</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35">
+        <v>520</v>
+      </c>
+      <c r="F35" t="s">
+        <v>136</v>
+      </c>
+      <c r="G35" t="s">
+        <v>43</v>
+      </c>
+      <c r="H35">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36">
+        <v>56000</v>
+      </c>
+      <c r="D36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36">
+        <v>1150000</v>
+      </c>
+      <c r="F36" t="s">
         <v>10</v>
       </c>
-      <c r="E31">
+      <c r="G36" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B37" t="s">
+        <v>140</v>
+      </c>
+      <c r="C37">
+        <v>22100</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37">
+        <v>1000</v>
+      </c>
+      <c r="F37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>141</v>
+      </c>
+      <c r="B38" t="s">
+        <v>142</v>
+      </c>
+      <c r="C38">
+        <v>56800</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38">
+        <v>1200</v>
+      </c>
+      <c r="F38" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" t="s">
+        <v>144</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39">
+        <v>35000</v>
+      </c>
+      <c r="D39" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39">
+        <v>820000</v>
+      </c>
+      <c r="F39" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40">
+        <v>29120</v>
+      </c>
+      <c r="D40" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40">
+        <v>780</v>
+      </c>
+      <c r="F40" t="s">
+        <v>149</v>
+      </c>
+      <c r="G40" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" t="s">
+        <v>151</v>
+      </c>
+      <c r="C41">
+        <v>29600</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>1250</v>
+      </c>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" t="s">
+        <v>153</v>
+      </c>
+      <c r="C42">
+        <v>22300</v>
+      </c>
+      <c r="D42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42">
+        <v>980000</v>
+      </c>
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+      <c r="G42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42">
+        <v>68000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43">
+        <v>29200</v>
+      </c>
+      <c r="D43" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43">
+        <v>2800</v>
+      </c>
+      <c r="F43" t="s">
+        <v>156</v>
+      </c>
+      <c r="G43" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44">
+        <v>29000</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+      <c r="E44">
+        <v>400</v>
+      </c>
+      <c r="F44" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" t="s">
+        <v>160</v>
+      </c>
+      <c r="H44">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45">
+        <v>35700</v>
+      </c>
+      <c r="D45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>720000</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
+      </c>
+      <c r="G45" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46">
+        <v>22400</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46">
+        <v>1900</v>
+      </c>
+      <c r="F46" t="s">
+        <v>165</v>
+      </c>
+      <c r="G46" t="s">
+        <v>46</v>
+      </c>
+      <c r="H46">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>166</v>
+      </c>
+      <c r="B47" t="s">
+        <v>167</v>
+      </c>
+      <c r="C47">
+        <v>56000</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47">
+        <v>1600</v>
+      </c>
+      <c r="F47" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" t="s">
+        <v>48</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>168</v>
+      </c>
+      <c r="B48" t="s">
+        <v>169</v>
+      </c>
+      <c r="C48">
+        <v>22100</v>
+      </c>
+      <c r="D48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48">
+        <v>1000000</v>
+      </c>
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="G48" t="s">
+        <v>27</v>
+      </c>
+      <c r="H48">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>170</v>
+      </c>
+      <c r="B49" t="s">
+        <v>171</v>
+      </c>
+      <c r="C49">
+        <v>56800</v>
+      </c>
+      <c r="D49" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49">
+        <v>950</v>
+      </c>
+      <c r="F49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>172</v>
+      </c>
+      <c r="B50" t="s">
+        <v>173</v>
+      </c>
+      <c r="C50">
+        <v>35000</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50">
+        <v>800</v>
+      </c>
+      <c r="F50" t="s">
+        <v>80</v>
+      </c>
+      <c r="G50" t="s">
+        <v>121</v>
+      </c>
+      <c r="H50">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51" t="s">
+        <v>175</v>
+      </c>
+      <c r="C51">
+        <v>29120</v>
+      </c>
+      <c r="D51" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51">
+        <v>1120000</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+      <c r="G51" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51">
+        <v>88000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52">
+        <v>29600</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52">
+        <v>2400</v>
+      </c>
+      <c r="F52" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" t="s">
+        <v>32</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" t="s">
+        <v>179</v>
+      </c>
+      <c r="C53">
+        <v>22300</v>
+      </c>
+      <c r="D53" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53">
+        <v>580</v>
+      </c>
+      <c r="F53" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" t="s">
+        <v>44</v>
+      </c>
+      <c r="H53">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>180</v>
+      </c>
+      <c r="B54" t="s">
+        <v>181</v>
+      </c>
+      <c r="C54">
+        <v>29200</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54">
+        <v>1450</v>
+      </c>
+      <c r="F54" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55">
+        <v>29000</v>
+      </c>
+      <c r="D55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55">
+        <v>840000</v>
+      </c>
+      <c r="F55" t="s">
+        <v>67</v>
+      </c>
+      <c r="G55" t="s">
+        <v>37</v>
+      </c>
+      <c r="H55">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>184</v>
+      </c>
+      <c r="B56" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56">
+        <v>35700</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56">
+        <v>1900</v>
+      </c>
+      <c r="F56" t="s">
+        <v>186</v>
+      </c>
+      <c r="G56" t="s">
+        <v>40</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>187</v>
+      </c>
+      <c r="B57" t="s">
+        <v>188</v>
+      </c>
+      <c r="C57">
+        <v>22400</v>
+      </c>
+      <c r="D57" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57">
+        <v>700</v>
+      </c>
+      <c r="F57" t="s">
+        <v>189</v>
+      </c>
+      <c r="G57" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>190</v>
+      </c>
+      <c r="B58" t="s">
+        <v>191</v>
+      </c>
+      <c r="C58">
+        <v>56000</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58">
+        <v>1150</v>
+      </c>
+      <c r="F58" t="s">
+        <v>106</v>
+      </c>
+      <c r="G58" t="s">
+        <v>49</v>
+      </c>
+      <c r="H58">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>192</v>
+      </c>
+      <c r="B59" t="s">
+        <v>193</v>
+      </c>
+      <c r="C59">
+        <v>22100</v>
+      </c>
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59">
+        <v>970000</v>
+      </c>
+      <c r="F59" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" t="s">
+        <v>32</v>
+      </c>
+      <c r="H59">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>194</v>
+      </c>
+      <c r="B60" t="s">
+        <v>195</v>
+      </c>
+      <c r="C60">
+        <v>56800</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60">
+        <v>1300</v>
+      </c>
+      <c r="F60" t="s">
+        <v>55</v>
+      </c>
+      <c r="G60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>196</v>
+      </c>
+      <c r="B61" t="s">
+        <v>197</v>
+      </c>
+      <c r="C61">
+        <v>35000</v>
+      </c>
+      <c r="D61" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61">
+        <v>880</v>
+      </c>
+      <c r="F61" t="s">
+        <v>80</v>
+      </c>
+      <c r="G61" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>198</v>
+      </c>
+      <c r="B62" t="s">
+        <v>199</v>
+      </c>
+      <c r="C62">
+        <v>29120</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62">
+        <v>1700</v>
+      </c>
+      <c r="F62" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>200</v>
+      </c>
+      <c r="B63" t="s">
+        <v>201</v>
+      </c>
+      <c r="C63">
+        <v>29600</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63">
+        <v>740000</v>
+      </c>
+      <c r="F63" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" t="s">
+        <v>203</v>
+      </c>
+      <c r="C64">
+        <v>22300</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64">
+        <v>2600</v>
+      </c>
+      <c r="F64" t="s">
+        <v>50</v>
+      </c>
+      <c r="G64" t="s">
+        <v>51</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>204</v>
+      </c>
+      <c r="B65" t="s">
+        <v>205</v>
+      </c>
+      <c r="C65">
+        <v>29200</v>
+      </c>
+      <c r="D65" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65">
+        <v>420</v>
+      </c>
+      <c r="F65" t="s">
+        <v>206</v>
+      </c>
+      <c r="G65" t="s">
+        <v>144</v>
+      </c>
+      <c r="H65">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>207</v>
+      </c>
+      <c r="B66" t="s">
+        <v>208</v>
+      </c>
+      <c r="C66">
+        <v>29000</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66">
+        <v>1350</v>
+      </c>
+      <c r="F66" t="s">
+        <v>96</v>
+      </c>
+      <c r="G66" t="s">
+        <v>32</v>
+      </c>
+      <c r="H66">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>209</v>
+      </c>
+      <c r="B67" t="s">
+        <v>210</v>
+      </c>
+      <c r="C67">
+        <v>35700</v>
+      </c>
+      <c r="D67" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67">
+        <v>1020000</v>
+      </c>
+      <c r="F67" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" t="s">
+        <v>54</v>
+      </c>
+      <c r="H67">
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>211</v>
+      </c>
+      <c r="B68" t="s">
+        <v>212</v>
+      </c>
+      <c r="C68">
+        <v>22400</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68">
+        <v>1700</v>
+      </c>
+      <c r="F68" t="s">
+        <v>213</v>
+      </c>
+      <c r="G68" t="s">
+        <v>29</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>214</v>
+      </c>
+      <c r="B69" t="s">
+        <v>215</v>
+      </c>
+      <c r="C69">
+        <v>56000</v>
+      </c>
+      <c r="D69" t="s">
+        <v>17</v>
+      </c>
+      <c r="E69">
+        <v>660</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" t="s">
+        <v>44</v>
+      </c>
+      <c r="H69">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>216</v>
+      </c>
+      <c r="B70" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70">
+        <v>22100</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70">
+        <v>1550</v>
+      </c>
+      <c r="F70" t="s">
+        <v>73</v>
+      </c>
+      <c r="G70" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>218</v>
+      </c>
+      <c r="B71" t="s">
+        <v>219</v>
+      </c>
+      <c r="C71">
+        <v>56800</v>
+      </c>
+      <c r="D71" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71">
+        <v>890000</v>
+      </c>
+      <c r="F71" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" t="s">
+        <v>40</v>
+      </c>
+      <c r="H71">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>220</v>
+      </c>
+      <c r="B72" t="s">
+        <v>221</v>
+      </c>
+      <c r="C72">
+        <v>35000</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72">
+        <v>2100</v>
+      </c>
+      <c r="F72" t="s">
+        <v>133</v>
+      </c>
+      <c r="G72" t="s">
+        <v>37</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>222</v>
+      </c>
+      <c r="B73" t="s">
+        <v>223</v>
+      </c>
+      <c r="C73">
+        <v>29120</v>
+      </c>
+      <c r="D73" t="s">
+        <v>17</v>
+      </c>
+      <c r="E73">
+        <v>500</v>
+      </c>
+      <c r="F73" t="s">
+        <v>224</v>
+      </c>
+      <c r="G73" t="s">
+        <v>121</v>
+      </c>
+      <c r="H73">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>225</v>
+      </c>
+      <c r="B74" t="s">
+        <v>226</v>
+      </c>
+      <c r="C74">
+        <v>29600</v>
+      </c>
+      <c r="D74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74">
+        <v>1200</v>
+      </c>
+      <c r="F74" t="s">
+        <v>65</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>227</v>
+      </c>
+      <c r="B75" t="s">
+        <v>228</v>
+      </c>
+      <c r="C75">
+        <v>22300</v>
+      </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75">
         <v>1180000</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F75" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>229</v>
+      </c>
+      <c r="B76" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76">
+        <v>29200</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76">
+        <v>2900</v>
+      </c>
+      <c r="F76" t="s">
+        <v>87</v>
+      </c>
+      <c r="G76" t="s">
+        <v>58</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>231</v>
+      </c>
+      <c r="B77" t="s">
+        <v>232</v>
+      </c>
+      <c r="C77">
+        <v>29000</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
+      </c>
+      <c r="E77">
+        <v>760</v>
+      </c>
+      <c r="F77" t="s">
+        <v>47</v>
+      </c>
+      <c r="G77" t="s">
+        <v>54</v>
+      </c>
+      <c r="H77">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C78">
+        <v>35700</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78">
+        <v>1000</v>
+      </c>
+      <c r="F78" t="s">
+        <v>39</v>
+      </c>
+      <c r="G78" t="s">
+        <v>49</v>
+      </c>
+      <c r="H78">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>235</v>
+      </c>
+      <c r="B79" t="s">
+        <v>236</v>
+      </c>
+      <c r="C79">
+        <v>22400</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79">
+        <v>650000</v>
+      </c>
+      <c r="F79" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" t="s">
+        <v>56</v>
+      </c>
+      <c r="H79">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>237</v>
+      </c>
+      <c r="B80" t="s">
+        <v>238</v>
+      </c>
+      <c r="C80">
+        <v>56000</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80">
+        <v>1400</v>
+      </c>
+      <c r="F80" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80" t="s">
+        <v>43</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>239</v>
+      </c>
+      <c r="B81" t="s">
+        <v>240</v>
+      </c>
+      <c r="C81">
+        <v>22100</v>
+      </c>
+      <c r="D81" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81">
+        <v>820</v>
+      </c>
+      <c r="F81" t="s">
+        <v>149</v>
+      </c>
+      <c r="G81" t="s">
+        <v>32</v>
+      </c>
+      <c r="H81">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" t="s">
+        <v>242</v>
+      </c>
+      <c r="C82">
+        <v>56800</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82">
+        <v>1450</v>
+      </c>
+      <c r="F82" t="s">
+        <v>118</v>
+      </c>
+      <c r="G82" t="s">
         <v>11</v>
       </c>
-      <c r="G31" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31">
-        <v>95000</v>
+      <c r="H82">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" t="s">
+        <v>244</v>
+      </c>
+      <c r="C83">
+        <v>35000</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83">
+        <v>930000</v>
+      </c>
+      <c r="F83" t="s">
+        <v>31</v>
+      </c>
+      <c r="G83" t="s">
+        <v>24</v>
+      </c>
+      <c r="H83">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>245</v>
+      </c>
+      <c r="B84" t="s">
+        <v>246</v>
+      </c>
+      <c r="C84">
+        <v>29120</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84">
+        <v>2300</v>
+      </c>
+      <c r="F84" t="s">
+        <v>41</v>
+      </c>
+      <c r="G84" t="s">
+        <v>27</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>247</v>
+      </c>
+      <c r="B85" t="s">
+        <v>248</v>
+      </c>
+      <c r="C85">
+        <v>29600</v>
+      </c>
+      <c r="D85" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85">
+        <v>480</v>
+      </c>
+      <c r="F85" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" t="s">
+        <v>56</v>
+      </c>
+      <c r="H85">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>249</v>
+      </c>
+      <c r="B86" t="s">
+        <v>250</v>
+      </c>
+      <c r="C86">
+        <v>22300</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86">
+        <v>1850</v>
+      </c>
+      <c r="F86" t="s">
+        <v>165</v>
+      </c>
+      <c r="G86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>251</v>
+      </c>
+      <c r="B87" t="s">
+        <v>252</v>
+      </c>
+      <c r="C87">
+        <v>29200</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87">
+        <v>1080000</v>
+      </c>
+      <c r="F87" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" t="s">
+        <v>51</v>
+      </c>
+      <c r="H87">
+        <v>82000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>253</v>
+      </c>
+      <c r="B88" t="s">
+        <v>254</v>
+      </c>
+      <c r="C88">
+        <v>29000</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88">
+        <v>1500</v>
+      </c>
+      <c r="F88" t="s">
+        <v>38</v>
+      </c>
+      <c r="G88" t="s">
+        <v>56</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>255</v>
+      </c>
+      <c r="B89" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89">
+        <v>35700</v>
+      </c>
+      <c r="D89" t="s">
+        <v>17</v>
+      </c>
+      <c r="E89">
+        <v>920</v>
+      </c>
+      <c r="F89" t="s">
+        <v>113</v>
+      </c>
+      <c r="G89" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>257</v>
+      </c>
+      <c r="B90" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90">
+        <v>22400</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90">
+        <v>750</v>
+      </c>
+      <c r="F90" t="s">
+        <v>47</v>
+      </c>
+      <c r="G90" t="s">
+        <v>144</v>
+      </c>
+      <c r="H90">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>259</v>
+      </c>
+      <c r="B91" t="s">
+        <v>260</v>
+      </c>
+      <c r="C91">
+        <v>56000</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91">
+        <v>770000</v>
+      </c>
+      <c r="F91" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" t="s">
+        <v>44</v>
+      </c>
+      <c r="H91">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>261</v>
+      </c>
+      <c r="B92" t="s">
+        <v>262</v>
+      </c>
+      <c r="C92">
+        <v>22100</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92">
+        <v>2700</v>
+      </c>
+      <c r="F92" t="s">
+        <v>156</v>
+      </c>
+      <c r="G92" t="s">
+        <v>21</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>263</v>
+      </c>
+      <c r="B93" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93">
+        <v>56800</v>
+      </c>
+      <c r="D93" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93">
+        <v>620</v>
+      </c>
+      <c r="F93" t="s">
+        <v>126</v>
+      </c>
+      <c r="G93" t="s">
+        <v>15</v>
+      </c>
+      <c r="H93">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>265</v>
+      </c>
+      <c r="B94" t="s">
+        <v>266</v>
+      </c>
+      <c r="C94">
+        <v>35000</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94">
+        <v>1350</v>
+      </c>
+      <c r="F94" t="s">
+        <v>96</v>
+      </c>
+      <c r="G94" t="s">
+        <v>54</v>
+      </c>
+      <c r="H94">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>267</v>
+      </c>
+      <c r="B95" t="s">
+        <v>268</v>
+      </c>
+      <c r="C95">
+        <v>29120</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95">
+        <v>860000</v>
+      </c>
+      <c r="F95" t="s">
+        <v>67</v>
+      </c>
+      <c r="G95" t="s">
+        <v>37</v>
+      </c>
+      <c r="H95">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>269</v>
+      </c>
+      <c r="B96" t="s">
+        <v>270</v>
+      </c>
+      <c r="C96">
+        <v>29600</v>
+      </c>
+      <c r="D96" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96">
+        <v>1100</v>
+      </c>
+      <c r="F96" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" t="s">
+        <v>271</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>272</v>
+      </c>
+      <c r="B97" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97">
+        <v>22300</v>
+      </c>
+      <c r="D97" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97">
+        <v>800</v>
+      </c>
+      <c r="F97" t="s">
+        <v>47</v>
+      </c>
+      <c r="G97" t="s">
+        <v>27</v>
+      </c>
+      <c r="H97">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>274</v>
+      </c>
+      <c r="B98" t="s">
+        <v>275</v>
+      </c>
+      <c r="C98">
+        <v>29200</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98">
+        <v>1100</v>
+      </c>
+      <c r="F98" t="s">
+        <v>106</v>
+      </c>
+      <c r="G98" t="s">
+        <v>44</v>
+      </c>
+      <c r="H98">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>276</v>
+      </c>
+      <c r="B99" t="s">
+        <v>277</v>
+      </c>
+      <c r="C99">
+        <v>29000</v>
+      </c>
+      <c r="D99" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99">
+        <v>1250000</v>
+      </c>
+      <c r="F99" t="s">
+        <v>90</v>
+      </c>
+      <c r="G99" t="s">
+        <v>278</v>
+      </c>
+      <c r="H99">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>279</v>
+      </c>
+      <c r="B100" t="s">
+        <v>280</v>
+      </c>
+      <c r="C100">
+        <v>35700</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100">
+        <v>1900</v>
+      </c>
+      <c r="F100" t="s">
+        <v>186</v>
+      </c>
+      <c r="G100" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>281</v>
+      </c>
+      <c r="B101" t="s">
+        <v>282</v>
+      </c>
+      <c r="C101">
+        <v>22400</v>
+      </c>
+      <c r="D101" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101">
+        <v>540</v>
+      </c>
+      <c r="F101" t="s">
+        <v>63</v>
+      </c>
+      <c r="G101" t="s">
+        <v>121</v>
+      </c>
+      <c r="H101">
+        <v>900</v>
       </c>
     </row>
   </sheetData>
